--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA291"/>
+  <dimension ref="A1:AA292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -31526,6 +31526,111 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Mediterranean Foods Limited</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Mediterranean Foods Limited</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>80795</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Christchurch</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>322 Tuam Street</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr"/>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>https://mediterraneanfoods.co.nz, https://shoponline.medifoods.co.nz</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>info@med-foods.co.nz</t>
+        </is>
+      </c>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>+64 3 379 5122</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>967280</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-mediterranean-food-company/</t>
+        </is>
+      </c>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MedFoodsChCh/</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mediterraneanfoods.co.nz/</t>
+        </is>
+      </c>
+      <c r="U292" s="2" t="inlineStr"/>
+      <c r="V292" s="2" t="inlineStr"/>
+      <c r="W292" s="2" t="inlineStr">
+        <is>
+          <t>Erika Deffendi</t>
+        </is>
+      </c>
+      <c r="X292" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y292" s="2" t="inlineStr"/>
+      <c r="Z292" s="2" t="inlineStr"/>
+      <c r="AA292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erika-deffendi-85861b174/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA292"/>
+  <dimension ref="A1:AA293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -31631,6 +31631,111 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Mediterranean Foods Limited</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Mediterranean Foods Limited</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>80795</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>Christchurch</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>322 Tuam Street</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr"/>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>https://mediterraneanfoods.co.nz, https://shoponline.medifoods.co.nz</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr"/>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>info@med-foods.co.nz</t>
+        </is>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>+64 3 379 5122</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>967280</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-mediterranean-food-company/</t>
+        </is>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MedFoodsChCh/</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mediterraneanfoods.co.nz/</t>
+        </is>
+      </c>
+      <c r="U293" s="2" t="inlineStr"/>
+      <c r="V293" s="2" t="inlineStr"/>
+      <c r="W293" s="2" t="inlineStr">
+        <is>
+          <t>Erika Deffendi</t>
+        </is>
+      </c>
+      <c r="X293" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y293" s="2" t="inlineStr"/>
+      <c r="Z293" s="2" t="inlineStr"/>
+      <c r="AA293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erika-deffendi-85861b174/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA293"/>
+  <dimension ref="A1:AA294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -31736,6 +31736,111 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Mediterranean Foods Limited</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Mediterranean Foods Limited</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>80795</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Christchurch</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>322 Tuam Street</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr"/>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>https://mediterraneanfoods.co.nz, https://shoponline.medifoods.co.nz</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>info@med-foods.co.nz</t>
+        </is>
+      </c>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>+64 3 379 5122</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>967280</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-mediterranean-food-company/</t>
+        </is>
+      </c>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MedFoodsChCh/</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mediterraneanfoods.co.nz/</t>
+        </is>
+      </c>
+      <c r="U294" s="2" t="inlineStr"/>
+      <c r="V294" s="2" t="inlineStr"/>
+      <c r="W294" s="2" t="inlineStr">
+        <is>
+          <t>Erika Deffendi</t>
+        </is>
+      </c>
+      <c r="X294" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y294" s="2" t="inlineStr"/>
+      <c r="Z294" s="2" t="inlineStr"/>
+      <c r="AA294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erika-deffendi-85861b174/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA294"/>
+  <dimension ref="A1:AA297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -31841,6 +31841,273 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>DPR FINE WINE LIMITED</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr"/>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>167781</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>33 Tamahere Drive</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>https://finewines.co.nz</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr"/>
+      <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>1216988</t>
+        </is>
+      </c>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>derrick@lucia.co.nz</t>
+        </is>
+      </c>
+      <c r="O295" s="2" t="inlineStr"/>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>7509196</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="inlineStr"/>
+      <c r="S295" s="2" t="inlineStr"/>
+      <c r="T295" s="2" t="inlineStr"/>
+      <c r="U295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="inlineStr"/>
+      <c r="W295" s="2" t="inlineStr">
+        <is>
+          <t>Derrick Liu</t>
+        </is>
+      </c>
+      <c r="X295" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y295" s="2" t="inlineStr"/>
+      <c r="Z295" s="2" t="inlineStr"/>
+      <c r="AA295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/derrick-j-liu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>FINOLA LIMITED</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr"/>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>167779</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr"/>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>22 Catherine St</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>https://finola.co.nz</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr"/>
+      <c r="K296" s="2" t="inlineStr"/>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
+          <t>442605</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>nathan@finola.co.nz</t>
+        </is>
+      </c>
+      <c r="O296" s="2" t="inlineStr"/>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>8178008</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr"/>
+      <c r="S296" s="2" t="inlineStr"/>
+      <c r="T296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="inlineStr"/>
+      <c r="W296" s="2" t="inlineStr">
+        <is>
+          <t>Nathan Nola</t>
+        </is>
+      </c>
+      <c r="X296" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y296" s="2" t="inlineStr"/>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>CASK INTERNATIONAL LIMITED</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr"/>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>167776</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr"/>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>98 Tramway Road</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>3214</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>https://cask.co.nz</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr"/>
+      <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>2222000</t>
+        </is>
+      </c>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>info@cask.co.nz</t>
+        </is>
+      </c>
+      <c r="O297" s="2" t="inlineStr"/>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>7184054</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr"/>
+      <c r="S297" s="2" t="inlineStr"/>
+      <c r="T297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="inlineStr"/>
+      <c r="W297" s="2" t="inlineStr">
+        <is>
+          <t>SUHAS ALLUMPURATH SUKUMARAN</t>
+        </is>
+      </c>
+      <c r="X297" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y297" s="2" t="inlineStr"/>
+      <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/suhas-allumpurath-sukumaran-a0b95210a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_New Zealand.xlsx
+++ b/BWI/bestwine_output/bestwine_New Zealand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA297"/>
+  <dimension ref="A1:AA298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32108,6 +32108,103 @@
         </is>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>SOIF LIMITED</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr"/>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>168202</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Blenheim</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Marlborough</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>1 Market Street</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.soif.co.nz</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr"/>
+      <c r="K298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>117158</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>arthur@soif.co.nz</t>
+        </is>
+      </c>
+      <c r="O298" s="2" t="inlineStr"/>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>9271560</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr"/>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61574078094072&amp;locale=en_GB#</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/soif.marketstreet</t>
+        </is>
+      </c>
+      <c r="U298" s="2" t="inlineStr"/>
+      <c r="V298" s="2" t="inlineStr"/>
+      <c r="W298" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Griffoul</t>
+        </is>
+      </c>
+      <c r="X298" s="2" t="inlineStr">
+        <is>
+          <t>Owner and Sommelier</t>
+        </is>
+      </c>
+      <c r="Y298" s="2" t="inlineStr"/>
+      <c r="Z298" s="2" t="inlineStr"/>
+      <c r="AA298" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
